--- a/Group-Split-Zscore.xlsx
+++ b/Group-Split-Zscore.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026-Human-Mice\Schoukroun-2026-Human-Mice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF589E4E-D5B1-4B82-96FF-AA52F40C7983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBAFCD5D-62A5-4463-B3FA-9C49B9A891A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{333C4A15-36FD-4A39-BDDE-7F64EF7BE38C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="58">
   <si>
     <t>id</t>
   </si>
@@ -204,6 +204,12 @@
   </si>
   <si>
     <t>Obesity</t>
+  </si>
+  <si>
+    <t>Vyvanse</t>
+  </si>
+  <si>
+    <t>Metformin</t>
   </si>
 </sst>
 </file>
@@ -575,10 +581,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FCEC350-0594-4575-8D2B-C7BC999CC977}">
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -594,8 +600,14 @@
       <c r="E1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -611,8 +623,14 @@
       <c r="E2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -628,8 +646,14 @@
       <c r="E3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -645,8 +669,14 @@
       <c r="E4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -662,8 +692,14 @@
       <c r="E5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -679,8 +715,14 @@
       <c r="E6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -696,8 +738,14 @@
       <c r="E7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -713,8 +761,14 @@
       <c r="E8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -730,8 +784,14 @@
       <c r="E9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -747,8 +807,14 @@
       <c r="E10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -764,8 +830,14 @@
       <c r="E11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -781,8 +853,14 @@
       <c r="E12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -798,8 +876,14 @@
       <c r="E13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -815,8 +899,14 @@
       <c r="E14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -832,8 +922,14 @@
       <c r="E15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -849,8 +945,14 @@
       <c r="E16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -866,8 +968,14 @@
       <c r="E17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -883,8 +991,14 @@
       <c r="E18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -900,8 +1014,14 @@
       <c r="E19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -917,8 +1037,14 @@
       <c r="E20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -934,8 +1060,14 @@
       <c r="E21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -951,8 +1083,14 @@
       <c r="E22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -968,8 +1106,14 @@
       <c r="E23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -985,8 +1129,14 @@
       <c r="E24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -1002,8 +1152,14 @@
       <c r="E25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -1019,8 +1175,14 @@
       <c r="E26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -1036,8 +1198,14 @@
       <c r="E27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -1053,8 +1221,14 @@
       <c r="E28">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -1070,8 +1244,14 @@
       <c r="E29">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -1087,8 +1267,14 @@
       <c r="E30">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -1104,8 +1290,14 @@
       <c r="E31">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -1121,8 +1313,14 @@
       <c r="E32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -1138,8 +1336,14 @@
       <c r="E33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>33</v>
       </c>
@@ -1155,8 +1359,14 @@
       <c r="E34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>34</v>
       </c>
@@ -1172,8 +1382,14 @@
       <c r="E35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>35</v>
       </c>
@@ -1189,8 +1405,14 @@
       <c r="E36">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>36</v>
       </c>
@@ -1206,8 +1428,14 @@
       <c r="E37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>37</v>
       </c>
@@ -1223,8 +1451,14 @@
       <c r="E38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>38</v>
       </c>
@@ -1240,8 +1474,14 @@
       <c r="E39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>39</v>
       </c>
@@ -1257,8 +1497,14 @@
       <c r="E40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>40</v>
       </c>
@@ -1274,8 +1520,14 @@
       <c r="E41">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>41</v>
       </c>
@@ -1291,8 +1543,14 @@
       <c r="E42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>42</v>
       </c>
@@ -1308,8 +1566,14 @@
       <c r="E43">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>43</v>
       </c>
@@ -1325,8 +1589,14 @@
       <c r="E44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>44</v>
       </c>
@@ -1342,8 +1612,14 @@
       <c r="E45">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>45</v>
       </c>
@@ -1359,8 +1635,14 @@
       <c r="E46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>46</v>
       </c>
@@ -1376,8 +1658,14 @@
       <c r="E47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -1393,8 +1681,14 @@
       <c r="E48">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>48</v>
       </c>
@@ -1410,8 +1704,14 @@
       <c r="E49">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>49</v>
       </c>
@@ -1426,6 +1726,12 @@
       </c>
       <c r="E50">
         <v>1</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Group-Split-Zscore.xlsx
+++ b/Group-Split-Zscore.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026-Human-Mice\Schoukroun-2026-Human-Mice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBAFCD5D-62A5-4463-B3FA-9C49B9A891A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E06E8A-B5BB-423D-B944-FC96E81FC493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{333C4A15-36FD-4A39-BDDE-7F64EF7BE38C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="56">
   <si>
     <t>id</t>
   </si>
@@ -198,12 +198,6 @@
   </si>
   <si>
     <t xml:space="preserve">BMI (kg.m-2) </t>
-  </si>
-  <si>
-    <t>BMI (Z-score)</t>
-  </si>
-  <si>
-    <t>Obesity</t>
   </si>
   <si>
     <t>Vyvanse</t>
@@ -581,10 +575,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FCEC350-0594-4575-8D2B-C7BC999CC977}">
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -600,14 +594,8 @@
       <c r="E1" t="s">
         <v>55</v>
       </c>
-      <c r="F1" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -618,19 +606,13 @@
         <v>29</v>
       </c>
       <c r="D2">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -641,19 +623,13 @@
         <v>29.8</v>
       </c>
       <c r="D3">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -664,19 +640,13 @@
         <v>24.4</v>
       </c>
       <c r="D4">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -687,19 +657,13 @@
         <v>29.862258950000001</v>
       </c>
       <c r="D5">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -710,19 +674,13 @@
         <v>46.721763090000003</v>
       </c>
       <c r="D6">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -733,19 +691,13 @@
         <v>20.8</v>
       </c>
       <c r="D7">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -756,19 +708,13 @@
         <v>43.1</v>
       </c>
       <c r="D8">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -779,19 +725,13 @@
         <v>31.7</v>
       </c>
       <c r="D9">
-        <v>2.1800000000000002</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -802,19 +742,13 @@
         <v>19.3</v>
       </c>
       <c r="D10">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -825,19 +759,13 @@
         <v>35.78</v>
       </c>
       <c r="D11">
-        <v>2.09</v>
+        <v>1</v>
       </c>
       <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -848,19 +776,13 @@
         <v>45.16</v>
       </c>
       <c r="D12">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -871,19 +793,13 @@
         <v>35.93</v>
       </c>
       <c r="D13">
-        <v>2.2999999999999998</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -894,19 +810,13 @@
         <v>35</v>
       </c>
       <c r="D14">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -917,19 +827,13 @@
         <v>34.700000000000003</v>
       </c>
       <c r="D15">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>1</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -940,19 +844,13 @@
         <v>31.5</v>
       </c>
       <c r="D16">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -963,19 +861,13 @@
         <v>36.700000000000003</v>
       </c>
       <c r="D17">
-        <v>2.5299999999999998</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -986,19 +878,13 @@
         <v>24.1</v>
       </c>
       <c r="D18">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>1</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -1009,19 +895,13 @@
         <v>18.399999999999999</v>
       </c>
       <c r="D19">
-        <v>-0.42</v>
+        <v>0</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -1032,19 +912,13 @@
         <v>25.5</v>
       </c>
       <c r="D20">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>1</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -1055,19 +929,13 @@
         <v>21.6</v>
       </c>
       <c r="D21">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -1078,19 +946,13 @@
         <v>34.5</v>
       </c>
       <c r="D22">
-        <v>2.2400000000000002</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>1</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -1101,19 +963,13 @@
         <v>38.200000000000003</v>
       </c>
       <c r="D23">
-        <v>2.5299999999999998</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>1</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -1124,19 +980,13 @@
         <v>26.5</v>
       </c>
       <c r="D24">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>1</v>
-      </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -1147,19 +997,13 @@
         <v>19.710249059999999</v>
       </c>
       <c r="D25">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -1170,19 +1014,13 @@
         <v>20.152974650000001</v>
       </c>
       <c r="D26">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="E26">
         <v>0</v>
       </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -1193,19 +1031,13 @@
         <v>23.146335310000001</v>
       </c>
       <c r="D27">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="E27">
         <v>0</v>
       </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -1216,19 +1048,13 @@
         <v>28</v>
       </c>
       <c r="D28">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>1</v>
-      </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -1239,19 +1065,13 @@
         <v>50.3</v>
       </c>
       <c r="D29">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="E29">
-        <v>1</v>
-      </c>
-      <c r="F29">
-        <v>0</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -1262,19 +1082,13 @@
         <v>40.1</v>
       </c>
       <c r="D30">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="E30">
-        <v>1</v>
-      </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -1285,19 +1099,13 @@
         <v>26.7</v>
       </c>
       <c r="D31">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="E31">
-        <v>1</v>
-      </c>
-      <c r="F31">
-        <v>0</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -1308,19 +1116,13 @@
         <v>21.5</v>
       </c>
       <c r="D32">
-        <v>0.69</v>
+        <v>0</v>
       </c>
       <c r="E32">
         <v>0</v>
       </c>
-      <c r="F32">
-        <v>0</v>
-      </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -1331,19 +1133,13 @@
         <v>18.899999999999999</v>
       </c>
       <c r="D33">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="E33">
         <v>0</v>
       </c>
-      <c r="F33">
-        <v>0</v>
-      </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>33</v>
       </c>
@@ -1354,19 +1150,13 @@
         <v>18</v>
       </c>
       <c r="D34">
-        <v>-0.39</v>
+        <v>0</v>
       </c>
       <c r="E34">
         <v>0</v>
       </c>
-      <c r="F34">
-        <v>0</v>
-      </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>34</v>
       </c>
@@ -1377,19 +1167,13 @@
         <v>15.5</v>
       </c>
       <c r="D35">
-        <v>-1.25</v>
+        <v>0</v>
       </c>
       <c r="E35">
         <v>0</v>
       </c>
-      <c r="F35">
-        <v>0</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>35</v>
       </c>
@@ -1400,19 +1184,13 @@
         <v>32.700000000000003</v>
       </c>
       <c r="D36">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="E36">
-        <v>1</v>
-      </c>
-      <c r="F36">
-        <v>0</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>36</v>
       </c>
@@ -1423,19 +1201,13 @@
         <v>21.5</v>
       </c>
       <c r="D37">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="E37">
         <v>0</v>
       </c>
-      <c r="F37">
-        <v>0</v>
-      </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>37</v>
       </c>
@@ -1446,19 +1218,13 @@
         <v>17</v>
       </c>
       <c r="D38">
-        <v>-0.52</v>
+        <v>0</v>
       </c>
       <c r="E38">
         <v>0</v>
       </c>
-      <c r="F38">
-        <v>0</v>
-      </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>38</v>
       </c>
@@ -1469,19 +1235,13 @@
         <v>18.399999999999999</v>
       </c>
       <c r="D39">
-        <v>-0.35</v>
+        <v>0</v>
       </c>
       <c r="E39">
         <v>0</v>
       </c>
-      <c r="F39">
-        <v>0</v>
-      </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>39</v>
       </c>
@@ -1492,19 +1252,13 @@
         <v>21.1</v>
       </c>
       <c r="D40">
-        <v>0.89</v>
+        <v>0</v>
       </c>
       <c r="E40">
         <v>0</v>
       </c>
-      <c r="F40">
-        <v>0</v>
-      </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>40</v>
       </c>
@@ -1515,19 +1269,13 @@
         <v>50.9</v>
       </c>
       <c r="D41">
-        <v>2.62</v>
+        <v>1</v>
       </c>
       <c r="E41">
-        <v>1</v>
-      </c>
-      <c r="F41">
-        <v>1</v>
-      </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>41</v>
       </c>
@@ -1538,19 +1286,13 @@
         <v>19.2</v>
       </c>
       <c r="D42">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="E42">
         <v>0</v>
       </c>
-      <c r="F42">
-        <v>1</v>
-      </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>42</v>
       </c>
@@ -1561,19 +1303,13 @@
         <v>29.3</v>
       </c>
       <c r="D43">
-        <v>1.98</v>
+        <v>1</v>
       </c>
       <c r="E43">
-        <v>1</v>
-      </c>
-      <c r="F43">
-        <v>1</v>
-      </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>43</v>
       </c>
@@ -1584,19 +1320,13 @@
         <v>18.100000000000001</v>
       </c>
       <c r="D44">
-        <v>-0.13</v>
+        <v>0</v>
       </c>
       <c r="E44">
         <v>0</v>
       </c>
-      <c r="F44">
-        <v>0</v>
-      </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>44</v>
       </c>
@@ -1607,19 +1337,13 @@
         <v>26.6</v>
       </c>
       <c r="D45">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="E45">
-        <v>1</v>
-      </c>
-      <c r="F45">
-        <v>0</v>
-      </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>45</v>
       </c>
@@ -1630,19 +1354,13 @@
         <v>19.5</v>
       </c>
       <c r="D46">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="E46">
         <v>0</v>
       </c>
-      <c r="F46">
-        <v>0</v>
-      </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>46</v>
       </c>
@@ -1653,19 +1371,13 @@
         <v>24.9</v>
       </c>
       <c r="D47">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="E47">
         <v>0</v>
       </c>
-      <c r="F47">
-        <v>0</v>
-      </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -1676,19 +1388,13 @@
         <v>44.5</v>
       </c>
       <c r="D48">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="E48">
-        <v>1</v>
-      </c>
-      <c r="F48">
-        <v>0</v>
-      </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>48</v>
       </c>
@@ -1699,19 +1405,13 @@
         <v>45.6</v>
       </c>
       <c r="D49">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="E49">
-        <v>1</v>
-      </c>
-      <c r="F49">
-        <v>0</v>
-      </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>49</v>
       </c>
@@ -1722,15 +1422,9 @@
         <v>23.9</v>
       </c>
       <c r="D50">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="E50">
-        <v>1</v>
-      </c>
-      <c r="F50">
-        <v>0</v>
-      </c>
-      <c r="G50">
         <v>0</v>
       </c>
     </row>

--- a/Group-Split-Zscore.xlsx
+++ b/Group-Split-Zscore.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026-Human-Mice\Schoukroun-2026-Human-Mice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E06E8A-B5BB-423D-B944-FC96E81FC493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{11202F87-08B4-45B5-A79F-3A1B354D88C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{333C4A15-36FD-4A39-BDDE-7F64EF7BE38C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="62">
   <si>
     <t>id</t>
   </si>
@@ -204,13 +204,31 @@
   </si>
   <si>
     <t>Metformin</t>
+  </si>
+  <si>
+    <t>GT</t>
+  </si>
+  <si>
+    <t>Percentile</t>
+  </si>
+  <si>
+    <t>M-Obesity</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>NOTE</t>
+  </si>
+  <si>
+    <t>Muscular</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -218,13 +236,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -239,8 +270,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,10 +611,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FCEC350-0594-4575-8D2B-C7BC999CC977}">
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -594,8 +630,20 @@
       <c r="E1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -611,8 +659,17 @@
       <c r="E2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>96</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -628,8 +685,17 @@
       <c r="E3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>97</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -645,8 +711,17 @@
       <c r="E4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>84</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -662,8 +737,17 @@
       <c r="E5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>96.8</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -679,8 +763,17 @@
       <c r="E6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>99.9</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -688,7 +781,7 @@
         <v>52</v>
       </c>
       <c r="C7">
-        <v>20.8</v>
+        <v>24.4</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -696,42 +789,69 @@
       <c r="E7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>82</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8">
+      <c r="B8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="1">
         <v>43.1</v>
       </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9">
+      <c r="B9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="1">
         <v>31.7</v>
       </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="1">
+        <v>97.2</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -747,8 +867,17 @@
       <c r="E10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>24</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -756,7 +885,7 @@
         <v>51</v>
       </c>
       <c r="C11">
-        <v>35.78</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -764,59 +893,95 @@
       <c r="E11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11">
+        <v>98</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12">
+      <c r="B12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="1">
         <v>45.16</v>
       </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="1">
+        <v>93</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13">
+      <c r="B13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="1">
         <v>35.93</v>
       </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="D13" s="1">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13" s="1">
+        <v>98.6</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14">
+      <c r="B14" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="1">
         <v>35</v>
       </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" s="1">
+        <v>96.3</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -832,8 +997,17 @@
       <c r="E15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="1">
+        <v>99</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -849,25 +1023,43 @@
       <c r="E16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="F16" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" s="1">
+        <v>98.2</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="2">
         <v>36.700000000000003</v>
       </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2">
+        <v>99.2</v>
+      </c>
+      <c r="H17" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -883,8 +1075,17 @@
       <c r="E18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18" s="2">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2">
+        <v>90</v>
+      </c>
+      <c r="H18" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -900,25 +1101,43 @@
       <c r="E19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2">
+        <v>34</v>
+      </c>
+      <c r="H19" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20">
+      <c r="B20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="1">
         <v>25.5</v>
       </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D20" s="1">
+        <v>0</v>
+      </c>
+      <c r="E20" s="1">
+        <v>0</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G20" s="1">
+        <v>91</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -934,8 +1153,17 @@
       <c r="E21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2">
+        <v>67</v>
+      </c>
+      <c r="H21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -951,8 +1179,17 @@
       <c r="E22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G22" s="2">
+        <v>98.6</v>
+      </c>
+      <c r="H22" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -968,8 +1205,17 @@
       <c r="E23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G23" s="2">
+        <v>99.9</v>
+      </c>
+      <c r="H23" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -985,8 +1231,17 @@
       <c r="E24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G24" s="2">
+        <v>90.6</v>
+      </c>
+      <c r="H24" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -1002,8 +1257,17 @@
       <c r="E25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2">
+        <v>59.5</v>
+      </c>
+      <c r="H25" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -1019,8 +1283,17 @@
       <c r="E26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2">
+        <v>74</v>
+      </c>
+      <c r="H26" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -1036,8 +1309,17 @@
       <c r="E27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F27" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G27" s="2">
+        <v>90</v>
+      </c>
+      <c r="H27" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -1053,8 +1335,17 @@
       <c r="E28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F28" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G28" s="2">
+        <v>94</v>
+      </c>
+      <c r="H28" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -1070,8 +1361,17 @@
       <c r="E29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F29" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G29" s="2">
+        <v>99.99</v>
+      </c>
+      <c r="H29" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -1087,25 +1387,46 @@
       <c r="E30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="F30" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G30" s="2">
+        <v>99.92</v>
+      </c>
+      <c r="H30" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
-        <v>51</v>
-      </c>
-      <c r="C31">
+      <c r="B31" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" s="3">
         <v>26.7</v>
       </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D31" s="3">
+        <v>0</v>
+      </c>
+      <c r="E31" s="3">
+        <v>0</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G31" s="5">
+        <v>90</v>
+      </c>
+      <c r="H31" s="5">
+        <v>0</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -1121,8 +1442,17 @@
       <c r="E32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2">
+        <v>75</v>
+      </c>
+      <c r="H32" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -1138,8 +1468,17 @@
       <c r="E33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33" s="2">
+        <v>46</v>
+      </c>
+      <c r="H33" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>33</v>
       </c>
@@ -1155,8 +1494,17 @@
       <c r="E34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34" s="2">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="H34" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>34</v>
       </c>
@@ -1172,8 +1520,17 @@
       <c r="E35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35" s="2">
+        <v>10.4</v>
+      </c>
+      <c r="H35" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>35</v>
       </c>
@@ -1189,8 +1546,17 @@
       <c r="E36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F36" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G36" s="2">
+        <v>98</v>
+      </c>
+      <c r="H36" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>36</v>
       </c>
@@ -1206,8 +1572,17 @@
       <c r="E37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37" s="2">
+        <v>58</v>
+      </c>
+      <c r="H37" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>37</v>
       </c>
@@ -1223,8 +1598,17 @@
       <c r="E38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38" s="2">
+        <v>30</v>
+      </c>
+      <c r="H38" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>38</v>
       </c>
@@ -1240,8 +1624,17 @@
       <c r="E39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39" s="2">
+        <v>36.5</v>
+      </c>
+      <c r="H39" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>39</v>
       </c>
@@ -1257,8 +1650,17 @@
       <c r="E40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40" s="2">
+        <v>81</v>
+      </c>
+      <c r="H40" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>40</v>
       </c>
@@ -1274,8 +1676,17 @@
       <c r="E41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41" s="2">
+        <v>99</v>
+      </c>
+      <c r="H41" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>41</v>
       </c>
@@ -1291,8 +1702,17 @@
       <c r="E42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42" s="2">
+        <v>29</v>
+      </c>
+      <c r="H42" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>42</v>
       </c>
@@ -1308,8 +1728,17 @@
       <c r="E43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F43" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G43" s="2">
+        <v>97.1</v>
+      </c>
+      <c r="H43" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>43</v>
       </c>
@@ -1325,8 +1754,17 @@
       <c r="E44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44" s="2">
+        <v>44.9</v>
+      </c>
+      <c r="H44" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>44</v>
       </c>
@@ -1342,8 +1780,17 @@
       <c r="E45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F45" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G45" s="2">
+        <v>92.2</v>
+      </c>
+      <c r="H45" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>45</v>
       </c>
@@ -1359,8 +1806,17 @@
       <c r="E46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46" s="2">
+        <v>42.2</v>
+      </c>
+      <c r="H46" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>46</v>
       </c>
@@ -1376,8 +1832,17 @@
       <c r="E47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F47" s="1">
+        <v>0</v>
+      </c>
+      <c r="G47" s="2">
+        <v>81.7</v>
+      </c>
+      <c r="H47" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -1393,8 +1858,17 @@
       <c r="E48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F48" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G48" s="2">
+        <v>99.3</v>
+      </c>
+      <c r="H48" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>48</v>
       </c>
@@ -1410,8 +1884,17 @@
       <c r="E49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F49" t="s">
+        <v>59</v>
+      </c>
+      <c r="G49" s="2">
+        <v>99.8</v>
+      </c>
+      <c r="H49" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>49</v>
       </c>
@@ -1427,8 +1910,18 @@
       <c r="E50">
         <v>0</v>
       </c>
+      <c r="F50" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G50" s="2">
+        <v>85.7</v>
+      </c>
+      <c r="H50" s="2">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Group-Split-Zscore.xlsx
+++ b/Group-Split-Zscore.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026-Human-Mice\Schoukroun-2026-Human-Mice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{11202F87-08B4-45B5-A79F-3A1B354D88C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6A86CC1-6F46-40A0-8A37-0DE015B05091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{333C4A15-36FD-4A39-BDDE-7F64EF7BE38C}"/>
+    <workbookView xWindow="10380" yWindow="4275" windowWidth="12510" windowHeight="11325" xr2:uid="{333C4A15-36FD-4A39-BDDE-7F64EF7BE38C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -270,13 +270,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -923,10 +921,10 @@
         <v>59</v>
       </c>
       <c r="G12" s="1">
-        <v>93</v>
+        <v>99.2</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -1034,28 +1032,28 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="A17" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17">
         <v>36.700000000000003</v>
       </c>
-      <c r="D17" s="2">
-        <v>0</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0</v>
-      </c>
-      <c r="F17" s="2">
-        <v>1</v>
-      </c>
-      <c r="G17" s="2">
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
         <v>99.2</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17">
         <v>1</v>
       </c>
     </row>
@@ -1075,13 +1073,13 @@
       <c r="E18">
         <v>0</v>
       </c>
-      <c r="F18" s="2">
-        <v>1</v>
-      </c>
-      <c r="G18" s="2">
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
         <v>90</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18">
         <v>0</v>
       </c>
     </row>
@@ -1104,10 +1102,10 @@
       <c r="F19">
         <v>0</v>
       </c>
-      <c r="G19" s="2">
+      <c r="G19">
         <v>34</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19">
         <v>0</v>
       </c>
     </row>
@@ -1156,10 +1154,10 @@
       <c r="F21">
         <v>0</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G21">
         <v>67</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21">
         <v>0</v>
       </c>
     </row>
@@ -1182,10 +1180,10 @@
       <c r="F22" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G22" s="2">
+      <c r="G22">
         <v>98.6</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H22">
         <v>1</v>
       </c>
     </row>
@@ -1208,10 +1206,10 @@
       <c r="F23" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G23" s="2">
+      <c r="G23">
         <v>99.9</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23">
         <v>1</v>
       </c>
     </row>
@@ -1234,10 +1232,10 @@
       <c r="F24" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G24" s="2">
+      <c r="G24">
         <v>90.6</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24">
         <v>0</v>
       </c>
     </row>
@@ -1260,10 +1258,10 @@
       <c r="F25">
         <v>0</v>
       </c>
-      <c r="G25" s="2">
+      <c r="G25">
         <v>59.5</v>
       </c>
-      <c r="H25" s="2">
+      <c r="H25">
         <v>0</v>
       </c>
     </row>
@@ -1286,10 +1284,10 @@
       <c r="F26">
         <v>0</v>
       </c>
-      <c r="G26" s="2">
+      <c r="G26">
         <v>74</v>
       </c>
-      <c r="H26" s="2">
+      <c r="H26">
         <v>0</v>
       </c>
     </row>
@@ -1312,10 +1310,10 @@
       <c r="F27" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G27" s="2">
+      <c r="G27">
         <v>90</v>
       </c>
-      <c r="H27" s="2">
+      <c r="H27">
         <v>0</v>
       </c>
     </row>
@@ -1338,10 +1336,10 @@
       <c r="F28" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G28" s="2">
+      <c r="G28">
         <v>94</v>
       </c>
-      <c r="H28" s="2">
+      <c r="H28">
         <v>0</v>
       </c>
     </row>
@@ -1364,10 +1362,10 @@
       <c r="F29" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G29" s="2">
+      <c r="G29">
         <v>99.99</v>
       </c>
-      <c r="H29" s="2">
+      <c r="H29">
         <v>1</v>
       </c>
     </row>
@@ -1390,39 +1388,39 @@
       <c r="F30" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G30" s="2">
+      <c r="G30">
         <v>99.92</v>
       </c>
-      <c r="H30" s="2">
+      <c r="H30">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="2">
         <v>26.7</v>
       </c>
-      <c r="D31" s="3">
-        <v>0</v>
-      </c>
-      <c r="E31" s="3">
-        <v>0</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G31" s="5">
+      <c r="D31" s="2">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G31" s="2">
         <v>90</v>
       </c>
-      <c r="H31" s="5">
-        <v>0</v>
-      </c>
-      <c r="I31" s="3" t="s">
+      <c r="H31" s="2">
+        <v>0</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1445,10 +1443,10 @@
       <c r="F32">
         <v>0</v>
       </c>
-      <c r="G32" s="2">
+      <c r="G32">
         <v>75</v>
       </c>
-      <c r="H32" s="2">
+      <c r="H32">
         <v>0</v>
       </c>
     </row>
@@ -1471,10 +1469,10 @@
       <c r="F33">
         <v>0</v>
       </c>
-      <c r="G33" s="2">
+      <c r="G33">
         <v>46</v>
       </c>
-      <c r="H33" s="2">
+      <c r="H33">
         <v>0</v>
       </c>
     </row>
@@ -1497,10 +1495,10 @@
       <c r="F34">
         <v>0</v>
       </c>
-      <c r="G34" s="2">
+      <c r="G34">
         <v>34.700000000000003</v>
       </c>
-      <c r="H34" s="2">
+      <c r="H34">
         <v>0</v>
       </c>
     </row>
@@ -1523,10 +1521,10 @@
       <c r="F35">
         <v>0</v>
       </c>
-      <c r="G35" s="2">
+      <c r="G35">
         <v>10.4</v>
       </c>
-      <c r="H35" s="2">
+      <c r="H35">
         <v>0</v>
       </c>
     </row>
@@ -1549,10 +1547,10 @@
       <c r="F36" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G36" s="2">
+      <c r="G36">
         <v>98</v>
       </c>
-      <c r="H36" s="2">
+      <c r="H36">
         <v>1</v>
       </c>
     </row>
@@ -1575,10 +1573,10 @@
       <c r="F37">
         <v>0</v>
       </c>
-      <c r="G37" s="2">
+      <c r="G37">
         <v>58</v>
       </c>
-      <c r="H37" s="2">
+      <c r="H37">
         <v>0</v>
       </c>
     </row>
@@ -1601,10 +1599,10 @@
       <c r="F38">
         <v>0</v>
       </c>
-      <c r="G38" s="2">
+      <c r="G38">
         <v>30</v>
       </c>
-      <c r="H38" s="2">
+      <c r="H38">
         <v>0</v>
       </c>
     </row>
@@ -1627,10 +1625,10 @@
       <c r="F39">
         <v>0</v>
       </c>
-      <c r="G39" s="2">
+      <c r="G39">
         <v>36.5</v>
       </c>
-      <c r="H39" s="2">
+      <c r="H39">
         <v>0</v>
       </c>
     </row>
@@ -1653,10 +1651,10 @@
       <c r="F40">
         <v>0</v>
       </c>
-      <c r="G40" s="2">
+      <c r="G40">
         <v>81</v>
       </c>
-      <c r="H40" s="2">
+      <c r="H40">
         <v>0</v>
       </c>
     </row>
@@ -1679,10 +1677,10 @@
       <c r="F41">
         <v>1</v>
       </c>
-      <c r="G41" s="2">
+      <c r="G41">
         <v>99</v>
       </c>
-      <c r="H41" s="2">
+      <c r="H41">
         <v>1</v>
       </c>
     </row>
@@ -1705,10 +1703,10 @@
       <c r="F42">
         <v>0</v>
       </c>
-      <c r="G42" s="2">
+      <c r="G42">
         <v>29</v>
       </c>
-      <c r="H42" s="2">
+      <c r="H42">
         <v>0</v>
       </c>
     </row>
@@ -1731,10 +1729,10 @@
       <c r="F43" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G43" s="2">
+      <c r="G43">
         <v>97.1</v>
       </c>
-      <c r="H43" s="2">
+      <c r="H43">
         <v>0</v>
       </c>
     </row>
@@ -1757,10 +1755,10 @@
       <c r="F44">
         <v>0</v>
       </c>
-      <c r="G44" s="2">
+      <c r="G44">
         <v>44.9</v>
       </c>
-      <c r="H44" s="2">
+      <c r="H44">
         <v>0</v>
       </c>
     </row>
@@ -1783,10 +1781,10 @@
       <c r="F45" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G45" s="2">
+      <c r="G45">
         <v>92.2</v>
       </c>
-      <c r="H45" s="2">
+      <c r="H45">
         <v>0</v>
       </c>
     </row>
@@ -1809,10 +1807,10 @@
       <c r="F46">
         <v>0</v>
       </c>
-      <c r="G46" s="2">
+      <c r="G46">
         <v>42.2</v>
       </c>
-      <c r="H46" s="2">
+      <c r="H46">
         <v>0</v>
       </c>
     </row>
@@ -1835,10 +1833,10 @@
       <c r="F47" s="1">
         <v>0</v>
       </c>
-      <c r="G47" s="2">
+      <c r="G47">
         <v>81.7</v>
       </c>
-      <c r="H47" s="2">
+      <c r="H47">
         <v>0</v>
       </c>
     </row>
@@ -1861,10 +1859,10 @@
       <c r="F48" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G48" s="2">
+      <c r="G48">
         <v>99.3</v>
       </c>
-      <c r="H48" s="2">
+      <c r="H48">
         <v>1</v>
       </c>
     </row>
@@ -1887,10 +1885,10 @@
       <c r="F49" t="s">
         <v>59</v>
       </c>
-      <c r="G49" s="2">
+      <c r="G49">
         <v>99.8</v>
       </c>
-      <c r="H49" s="2">
+      <c r="H49">
         <v>1</v>
       </c>
     </row>
@@ -1913,10 +1911,10 @@
       <c r="F50" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G50" s="2">
+      <c r="G50">
         <v>85.7</v>
       </c>
-      <c r="H50" s="2">
+      <c r="H50">
         <v>0</v>
       </c>
     </row>

--- a/Group-Split-Zscore.xlsx
+++ b/Group-Split-Zscore.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026-Human-Mice\Schoukroun-2026-Human-Mice\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun-2026-Human-Mice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6A86CC1-6F46-40A0-8A37-0DE015B05091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3D26CB-AE48-4811-92F7-4294D267ACDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10380" yWindow="4275" windowWidth="12510" windowHeight="11325" xr2:uid="{333C4A15-36FD-4A39-BDDE-7F64EF7BE38C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{333C4A15-36FD-4A39-BDDE-7F64EF7BE38C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="63">
   <si>
     <t>id</t>
   </si>
@@ -222,6 +222,9 @@
   </si>
   <si>
     <t>Muscular</t>
+  </si>
+  <si>
+    <t>Age</t>
   </si>
 </sst>
 </file>
@@ -609,181 +612,202 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FCEC350-0594-4575-8D2B-C7BC999CC977}">
-  <dimension ref="A1:I50"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J50"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.6328125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" t="s">
         <v>50</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>53</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>54</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>55</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>56</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>57</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>58</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2">
+      <c r="B2">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2">
         <v>29</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
         <v>2</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>96</v>
       </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3">
+      <c r="B3">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3">
         <v>29.8</v>
       </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
         <v>2</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>97</v>
       </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
         <v>52</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>24.4</v>
       </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
         <v>84</v>
       </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5">
+      <c r="B5">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5">
         <v>29.862258950000001</v>
       </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
         <v>96.8</v>
       </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
         <v>52</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>46.721763090000003</v>
       </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
         <v>99.9</v>
       </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
         <v>52</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>24.4</v>
       </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
       <c r="E7">
         <v>0</v>
       </c>
@@ -791,77 +815,86 @@
         <v>0</v>
       </c>
       <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
         <v>82</v>
       </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="1">
+      <c r="B8" s="1">
+        <v>16</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="1">
         <v>43.1</v>
       </c>
-      <c r="D8" s="1">
-        <v>0</v>
-      </c>
       <c r="E8" s="1">
         <v>0</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G8" s="1">
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" s="1">
         <v>99.7</v>
       </c>
-      <c r="H8" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" s="1">
+      <c r="B9" s="1">
+        <v>15</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="1">
         <v>31.7</v>
       </c>
-      <c r="D9" s="1">
-        <v>0</v>
-      </c>
       <c r="E9" s="1">
         <v>0</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G9" s="1">
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="1">
         <v>97.2</v>
       </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10">
+      <c r="B10">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10">
         <v>19.3</v>
       </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
       <c r="E10">
         <v>0</v>
       </c>
@@ -869,233 +902,260 @@
         <v>0</v>
       </c>
       <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
         <v>24</v>
       </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11">
+      <c r="B11">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11">
         <v>35.200000000000003</v>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
       <c r="E11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
         <v>2</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>98</v>
       </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" s="1">
+      <c r="B12" s="1">
+        <v>17</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="1">
         <v>45.16</v>
       </c>
-      <c r="D12" s="1">
-        <v>0</v>
-      </c>
       <c r="E12" s="1">
         <v>0</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12" s="1">
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H12" s="1">
         <v>99.2</v>
       </c>
-      <c r="H12" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="1">
+      <c r="B13" s="1">
+        <v>16</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="1">
         <v>35.93</v>
       </c>
-      <c r="D13" s="1">
-        <v>0</v>
-      </c>
       <c r="E13" s="1">
         <v>0</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G13" s="1">
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H13" s="1">
         <v>98.6</v>
       </c>
-      <c r="H13" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" s="1">
+      <c r="B14" s="1">
+        <v>16</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="1">
         <v>35</v>
       </c>
-      <c r="D14" s="1">
-        <v>0</v>
-      </c>
       <c r="E14" s="1">
         <v>0</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G14" s="1">
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14" s="1">
         <v>96.3</v>
       </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1">
+        <v>15</v>
+      </c>
+      <c r="C15" t="s">
         <v>52</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>34.700000000000003</v>
       </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
       <c r="E15">
         <v>0</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G15" s="1">
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H15" s="1">
         <v>99</v>
       </c>
-      <c r="H15" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1">
+        <v>14</v>
+      </c>
+      <c r="C16" t="s">
         <v>52</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>31.5</v>
       </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
       <c r="E16">
         <v>0</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G16" s="1">
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H16" s="1">
         <v>98.2</v>
       </c>
-      <c r="H16" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
         <v>52</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>36.700000000000003</v>
       </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
         <v>99.2</v>
       </c>
-      <c r="H17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="1">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
         <v>52</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>24.1</v>
       </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
       <c r="E18">
         <v>0</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
         <v>90</v>
       </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19">
+      <c r="B19" s="1">
+        <v>15</v>
+      </c>
+      <c r="C19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19">
         <v>18.399999999999999</v>
       </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
       <c r="E19">
         <v>0</v>
       </c>
@@ -1103,51 +1163,57 @@
         <v>0</v>
       </c>
       <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
         <v>34</v>
       </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="1">
+      <c r="B20" s="1">
+        <v>15</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" s="1">
         <v>25.5</v>
       </c>
-      <c r="D20" s="1">
-        <v>0</v>
-      </c>
       <c r="E20" s="1">
         <v>0</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G20" s="1">
+      <c r="F20" s="1">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H20" s="1">
         <v>91</v>
       </c>
-      <c r="H20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21">
+      <c r="B21" s="1">
+        <v>15</v>
+      </c>
+      <c r="C21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21">
         <v>21.6</v>
       </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
       <c r="E21">
         <v>0</v>
       </c>
@@ -1155,103 +1221,115 @@
         <v>0</v>
       </c>
       <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
         <v>67</v>
       </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="1">
+        <v>15</v>
+      </c>
+      <c r="C22" t="s">
         <v>52</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>34.5</v>
       </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
       <c r="E22">
         <v>0</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G22">
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H22">
         <v>98.6</v>
       </c>
-      <c r="H22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
-        <v>51</v>
-      </c>
-      <c r="C23">
+      <c r="B23" s="1">
+        <v>17</v>
+      </c>
+      <c r="C23" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23">
         <v>38.200000000000003</v>
       </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
       <c r="E23">
         <v>0</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G23">
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H23">
         <v>99.9</v>
       </c>
-      <c r="H23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1">
+        <v>19</v>
+      </c>
+      <c r="C24" t="s">
         <v>52</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <v>26.5</v>
       </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
       <c r="E24">
         <v>0</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G24">
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H24">
         <v>90.6</v>
       </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25">
+      <c r="B25" s="1">
+        <v>13</v>
+      </c>
+      <c r="C25" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25">
         <v>19.710249059999999</v>
       </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
       <c r="E25">
         <v>0</v>
       </c>
@@ -1259,25 +1337,28 @@
         <v>0</v>
       </c>
       <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
         <v>59.5</v>
       </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="1">
+        <v>12</v>
+      </c>
+      <c r="C26" t="s">
         <v>52</v>
       </c>
-      <c r="C26">
+      <c r="D26">
         <v>20.152974650000001</v>
       </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
       <c r="E26">
         <v>0</v>
       </c>
@@ -1285,158 +1366,176 @@
         <v>0</v>
       </c>
       <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
         <v>74</v>
       </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="1">
+        <v>13</v>
+      </c>
+      <c r="C27" t="s">
         <v>52</v>
       </c>
-      <c r="C27">
+      <c r="D27">
         <v>23.146335310000001</v>
       </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
       <c r="E27">
         <v>0</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G27">
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H27">
         <v>90</v>
       </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
-        <v>51</v>
-      </c>
-      <c r="C28">
+      <c r="B28" s="1">
+        <v>15</v>
+      </c>
+      <c r="C28" t="s">
+        <v>51</v>
+      </c>
+      <c r="D28">
         <v>28</v>
       </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
       <c r="E28">
         <v>0</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G28">
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H28">
         <v>94</v>
       </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
-        <v>51</v>
-      </c>
-      <c r="C29">
+      <c r="B29" s="1">
+        <v>13</v>
+      </c>
+      <c r="C29" t="s">
+        <v>51</v>
+      </c>
+      <c r="D29">
         <v>50.3</v>
       </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
       <c r="E29">
         <v>0</v>
       </c>
-      <c r="F29" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G29">
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H29">
         <v>99.99</v>
       </c>
-      <c r="H29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
-        <v>51</v>
-      </c>
-      <c r="C30">
+      <c r="B30" s="1">
+        <v>13</v>
+      </c>
+      <c r="C30" t="s">
+        <v>51</v>
+      </c>
+      <c r="D30">
         <v>40.1</v>
       </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
       <c r="E30">
         <v>0</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G30">
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H30">
         <v>99.92</v>
       </c>
-      <c r="H30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="2">
+        <v>15</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C31" s="2">
+      <c r="D31" s="2">
         <v>26.7</v>
       </c>
-      <c r="D31" s="2">
-        <v>0</v>
-      </c>
       <c r="E31" s="2">
         <v>0</v>
       </c>
-      <c r="F31" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="G31" s="2">
+      <c r="F31" s="2">
+        <v>0</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H31" s="2">
         <v>90</v>
       </c>
-      <c r="H31" s="2">
-        <v>0</v>
-      </c>
-      <c r="I31" s="2" t="s">
+      <c r="I31" s="2">
+        <v>0</v>
+      </c>
+      <c r="J31" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
-        <v>51</v>
-      </c>
-      <c r="C32">
+      <c r="B32" s="1">
+        <v>14</v>
+      </c>
+      <c r="C32" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32">
         <v>21.5</v>
       </c>
-      <c r="D32">
-        <v>0</v>
-      </c>
       <c r="E32">
         <v>0</v>
       </c>
@@ -1444,25 +1543,28 @@
         <v>0</v>
       </c>
       <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
         <v>75</v>
       </c>
-      <c r="H32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
-        <v>51</v>
-      </c>
-      <c r="C33">
+      <c r="B33" s="1">
+        <v>13</v>
+      </c>
+      <c r="C33" t="s">
+        <v>51</v>
+      </c>
+      <c r="D33">
         <v>18.899999999999999</v>
       </c>
-      <c r="D33">
-        <v>0</v>
-      </c>
       <c r="E33">
         <v>0</v>
       </c>
@@ -1470,25 +1572,28 @@
         <v>0</v>
       </c>
       <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
         <v>46</v>
       </c>
-      <c r="H33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
-        <v>51</v>
-      </c>
-      <c r="C34">
+      <c r="B34" s="1">
+        <v>13</v>
+      </c>
+      <c r="C34" t="s">
+        <v>51</v>
+      </c>
+      <c r="D34">
         <v>18</v>
       </c>
-      <c r="D34">
-        <v>0</v>
-      </c>
       <c r="E34">
         <v>0</v>
       </c>
@@ -1496,25 +1601,28 @@
         <v>0</v>
       </c>
       <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
         <v>34.700000000000003</v>
       </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
-        <v>51</v>
-      </c>
-      <c r="C35">
+      <c r="B35" s="1">
+        <v>12</v>
+      </c>
+      <c r="C35" t="s">
+        <v>51</v>
+      </c>
+      <c r="D35">
         <v>15.5</v>
       </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
       <c r="E35">
         <v>0</v>
       </c>
@@ -1522,51 +1630,57 @@
         <v>0</v>
       </c>
       <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
         <v>10.4</v>
       </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
-        <v>51</v>
-      </c>
-      <c r="C36">
+      <c r="B36" s="1">
+        <v>14</v>
+      </c>
+      <c r="C36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D36">
         <v>32.700000000000003</v>
       </c>
-      <c r="D36">
-        <v>0</v>
-      </c>
       <c r="E36">
         <v>0</v>
       </c>
-      <c r="F36" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G36">
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H36">
         <v>98</v>
       </c>
-      <c r="H36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>36</v>
       </c>
-      <c r="B37" t="s">
-        <v>51</v>
-      </c>
-      <c r="C37">
+      <c r="B37" s="1">
+        <v>17</v>
+      </c>
+      <c r="C37" t="s">
+        <v>51</v>
+      </c>
+      <c r="D37">
         <v>21.5</v>
       </c>
-      <c r="D37">
-        <v>0</v>
-      </c>
       <c r="E37">
         <v>0</v>
       </c>
@@ -1574,25 +1688,28 @@
         <v>0</v>
       </c>
       <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
         <v>58</v>
       </c>
-      <c r="H37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
-        <v>51</v>
-      </c>
-      <c r="C38">
+      <c r="B38" s="1">
+        <v>13</v>
+      </c>
+      <c r="C38" t="s">
+        <v>51</v>
+      </c>
+      <c r="D38">
         <v>17</v>
       </c>
-      <c r="D38">
-        <v>0</v>
-      </c>
       <c r="E38">
         <v>0</v>
       </c>
@@ -1600,25 +1717,28 @@
         <v>0</v>
       </c>
       <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
         <v>30</v>
       </c>
-      <c r="H38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>38</v>
       </c>
-      <c r="B39" t="s">
-        <v>51</v>
-      </c>
-      <c r="C39">
+      <c r="B39" s="1">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>51</v>
+      </c>
+      <c r="D39">
         <v>18.399999999999999</v>
       </c>
-      <c r="D39">
-        <v>0</v>
-      </c>
       <c r="E39">
         <v>0</v>
       </c>
@@ -1626,25 +1746,28 @@
         <v>0</v>
       </c>
       <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
         <v>36.5</v>
       </c>
-      <c r="H39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
-        <v>51</v>
-      </c>
-      <c r="C40">
+      <c r="B40" s="1">
+        <v>13</v>
+      </c>
+      <c r="C40" t="s">
+        <v>51</v>
+      </c>
+      <c r="D40">
         <v>21.1</v>
       </c>
-      <c r="D40">
-        <v>0</v>
-      </c>
       <c r="E40">
         <v>0</v>
       </c>
@@ -1652,103 +1775,115 @@
         <v>0</v>
       </c>
       <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
         <v>81</v>
       </c>
-      <c r="H40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>40</v>
       </c>
-      <c r="B41" t="s">
-        <v>51</v>
-      </c>
-      <c r="C41">
+      <c r="B41" s="1">
+        <v>17</v>
+      </c>
+      <c r="C41" t="s">
+        <v>51</v>
+      </c>
+      <c r="D41">
         <v>50.9</v>
       </c>
-      <c r="D41">
-        <v>1</v>
-      </c>
       <c r="E41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41">
         <v>99</v>
       </c>
-      <c r="H41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>41</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="1">
+        <v>16</v>
+      </c>
+      <c r="C42" t="s">
         <v>52</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>19.2</v>
       </c>
-      <c r="D42">
-        <v>1</v>
-      </c>
       <c r="E42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42">
         <v>0</v>
       </c>
       <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
         <v>29</v>
       </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>42</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="1">
+        <v>14</v>
+      </c>
+      <c r="C43" t="s">
         <v>52</v>
       </c>
-      <c r="C43">
+      <c r="D43">
         <v>29.3</v>
       </c>
-      <c r="D43">
-        <v>1</v>
-      </c>
       <c r="E43">
-        <v>0</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G43">
+        <v>1</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H43">
         <v>97.1</v>
       </c>
-      <c r="H43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>43</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="1">
+        <v>12</v>
+      </c>
+      <c r="C44" t="s">
         <v>52</v>
       </c>
-      <c r="C44">
+      <c r="D44">
         <v>18.100000000000001</v>
       </c>
-      <c r="D44">
-        <v>0</v>
-      </c>
       <c r="E44">
         <v>0</v>
       </c>
@@ -1756,51 +1891,57 @@
         <v>0</v>
       </c>
       <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
         <v>44.9</v>
       </c>
-      <c r="H44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>44</v>
       </c>
-      <c r="B45" t="s">
-        <v>51</v>
-      </c>
-      <c r="C45">
+      <c r="B45" s="1">
+        <v>15</v>
+      </c>
+      <c r="C45" t="s">
+        <v>51</v>
+      </c>
+      <c r="D45">
         <v>26.6</v>
       </c>
-      <c r="D45">
-        <v>0</v>
-      </c>
       <c r="E45">
         <v>0</v>
       </c>
-      <c r="F45" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G45">
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H45">
         <v>92.2</v>
       </c>
-      <c r="H45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>45</v>
       </c>
-      <c r="B46" t="s">
-        <v>51</v>
-      </c>
-      <c r="C46">
+      <c r="B46" s="1">
+        <v>15</v>
+      </c>
+      <c r="C46" t="s">
+        <v>51</v>
+      </c>
+      <c r="D46">
         <v>19.5</v>
       </c>
-      <c r="D46">
-        <v>0</v>
-      </c>
       <c r="E46">
         <v>0</v>
       </c>
@@ -1808,113 +1949,128 @@
         <v>0</v>
       </c>
       <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
         <v>42.2</v>
       </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>46</v>
       </c>
-      <c r="B47" t="s">
-        <v>51</v>
-      </c>
-      <c r="C47">
+      <c r="B47" s="1">
+        <v>17</v>
+      </c>
+      <c r="C47" t="s">
+        <v>51</v>
+      </c>
+      <c r="D47">
         <v>24.9</v>
       </c>
-      <c r="D47">
-        <v>0</v>
-      </c>
       <c r="E47">
         <v>0</v>
       </c>
-      <c r="F47" s="1">
-        <v>0</v>
-      </c>
-      <c r="G47">
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0</v>
+      </c>
+      <c r="H47">
         <v>81.7</v>
       </c>
-      <c r="H47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>47</v>
       </c>
-      <c r="B48" t="s">
-        <v>51</v>
-      </c>
-      <c r="C48">
+      <c r="B48" s="1">
+        <v>17</v>
+      </c>
+      <c r="C48" t="s">
+        <v>51</v>
+      </c>
+      <c r="D48">
         <v>44.5</v>
       </c>
-      <c r="D48">
-        <v>0</v>
-      </c>
       <c r="E48">
         <v>0</v>
       </c>
-      <c r="F48" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G48">
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H48">
         <v>99.3</v>
       </c>
-      <c r="H48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>48</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="1">
+        <v>12</v>
+      </c>
+      <c r="C49" t="s">
         <v>52</v>
       </c>
-      <c r="C49">
+      <c r="D49">
         <v>45.6</v>
       </c>
-      <c r="D49">
-        <v>0</v>
-      </c>
       <c r="E49">
         <v>0</v>
       </c>
-      <c r="F49" t="s">
-        <v>59</v>
-      </c>
-      <c r="G49">
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49" t="s">
+        <v>59</v>
+      </c>
+      <c r="H49">
         <v>99.8</v>
       </c>
-      <c r="H49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>49</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="1">
+        <v>15</v>
+      </c>
+      <c r="C50" t="s">
         <v>52</v>
       </c>
-      <c r="C50">
+      <c r="D50">
         <v>23.9</v>
       </c>
-      <c r="D50">
-        <v>0</v>
-      </c>
       <c r="E50">
         <v>0</v>
       </c>
-      <c r="F50" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G50">
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H50">
         <v>85.7</v>
       </c>
-      <c r="H50">
+      <c r="I50">
         <v>0</v>
       </c>
     </row>
